--- a/papers/P003/P003_工程复现问题清单_v1.xlsx
+++ b/papers/P003/P003_工程复现问题清单_v1.xlsx
@@ -36,7 +36,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFF0F5FA"/>
+        <fgColor rgb="FFF1F5F9"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -55,13 +55,13 @@
   </cellStyleXfs>
   <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
+      <alignment wrapText="1" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
+      <alignment wrapText="1" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
+      <alignment wrapText="1" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -72,15 +72,15 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C8"/>
-  <sheetFormatPr defaultRowHeight="24"/>
+  <dimension ref="A1:C10"/>
+  <sheetFormatPr defaultRowHeight="25"/>
   <cols>
-    <col min="1" max="1" width="23" customWidth="1"/>
+    <col min="1" max="1" width="26" customWidth="1"/>
     <col min="2" max="2" width="54" customWidth="1"/>
-    <col min="3" max="3" width="101" customWidth="1"/>
+    <col min="3" max="3" width="103" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="35" customHeight="1">
+    <row r="1" ht="38" customHeight="1">
       <c r="A1" t="inlineStr" s="1">
         <is>
           <t xml:space="preserve">主题</t>
@@ -97,7 +97,7 @@
         </is>
       </c>
     </row>
-    <row r="2" ht="85" customHeight="1">
+    <row r="2" ht="93" customHeight="1">
       <c r="A2" t="inlineStr" s="0">
         <is>
           <t xml:space="preserve">初始研究假设</t>
@@ -114,112 +114,146 @@
         </is>
       </c>
     </row>
-    <row r="3" ht="85" customHeight="1">
+    <row r="3" ht="103" customHeight="1">
       <c r="A3" t="inlineStr" s="2">
         <is>
+          <t xml:space="preserve">Agent输入与上下文</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">市场知识、历史案例怎样进入Factor Agent？是否是结构化Prompt？</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">Idea Agent把研究方向或市场观察整理为“观察、知识、经济解释、实现规格”四部分假设；Factor Agent结合假设、金融算子库和成功/失败实现经验生成公式。论文说明了信息结构，但未从论文原版源码核实逐字Prompt装配，也没有P005式每日市场摘要器。</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="93" customHeight="1">
+      <c r="A4" t="inlineStr" s="0">
+        <is>
           <t xml:space="preserve">LLM与Agent分工</t>
         </is>
       </c>
-      <c r="B3" t="inlineStr" s="2">
+      <c r="B4" t="inlineStr" s="0">
         <is>
           <t xml:space="preserve">使用什么模型？三个Agent分别负责什么？</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr" s="2">
+      <c r="C4" t="inlineStr" s="0">
         <is>
           <t xml:space="preserve">论文实验使用GPT-3.5-turbo作为基础LLM；Idea提出假设，Factor构造多个因子，Eval负责评价与反馈。原文未报告通过微调更新这些Agent的模型参数。</t>
         </is>
       </c>
     </row>
-    <row r="4" ht="85" customHeight="1">
-      <c r="A4" t="inlineStr" s="0">
+    <row r="5" ht="93" customHeight="1">
+      <c r="A5" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">因子生成格式</t>
         </is>
       </c>
-      <c r="B4" t="inlineStr" s="0">
+      <c r="B5" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">Factor Agent怎么把Idea变成可执行因子？</t>
         </is>
       </c>
-      <c r="C4" t="inlineStr" s="0">
+      <c r="C5" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">调用金融算子库（如滚动均值、最高最低值、条件算子），把原始行情字段与算子组成符号表达式/AST计算树，而非直接自由生成完整Python程序；每个假设可对应多个候选。</t>
         </is>
       </c>
     </row>
-    <row r="5" ht="85" customHeight="1">
-      <c r="A5" t="inlineStr" s="2">
+    <row r="6" ht="93" customHeight="1">
+      <c r="A6" t="inlineStr" s="0">
         <is>
           <t xml:space="preserve">三项生成约束</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr" s="2">
+      <c r="B6" t="inlineStr" s="0">
         <is>
           <t xml:space="preserve">为什么说生成不是随便写公式？</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr" s="2">
+      <c r="C6" t="inlineStr" s="0">
         <is>
           <t xml:space="preserve">①原创性：将新因子AST与Alpha Zoo既有因子比较最大公共子树，抑制结构重复；②语义一致性：LLM分别判断假设→因子描述、描述→公式是否匹配；③复杂度：限制公式长度、参数与特征数量。</t>
         </is>
       </c>
     </row>
-    <row r="6" ht="85" customHeight="1">
-      <c r="A6" t="inlineStr" s="0">
+    <row r="7" ht="93" customHeight="1">
+      <c r="A7" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">质量评价</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr" s="0">
+      <c r="B7" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">Eval Agent具体评什么？</t>
         </is>
       </c>
-      <c r="C6" t="inlineStr" s="0">
+      <c r="C7" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">检查因子可执行性、数值稳定性，并通过历史数据检验预测力（IC/RankIC/ICIR）、收益和风险表现；论文采用Qlib回测。重点是实际计算指标，而非仅由LLM主观判断。</t>
         </is>
       </c>
     </row>
-    <row r="7" ht="85" customHeight="1">
-      <c r="A7" t="inlineStr" s="2">
+    <row r="8" ht="93" customHeight="1">
+      <c r="A8" t="inlineStr" s="0">
+        <is>
+          <t xml:space="preserve">单因子还是池级增益</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr" s="0">
+        <is>
+          <t xml:space="preserve">这是按单个因子质量筛选，还是按整池新增边际贡献筛选？</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr" s="0">
+        <is>
+          <t xml:space="preserve">主要检查各候选的AST原创性、假设对齐、复杂度和预测/收益/风险表现；Alpha Zoo用于结构相似度参照，成功失败结果用于经验反馈。论文没有说明使用P005那样的加权组合池评分差ΔΓ决定加入/替换。</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="93" customHeight="1">
+      <c r="A9" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">反馈与自迭代</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr" s="2">
+      <c r="B9" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">评价结果究竟怎样进入下一轮？</t>
         </is>
       </c>
-      <c r="C7" t="inlineStr" s="2">
+      <c r="C9" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">Eval汇总成功/失败及表现反馈给Idea以改写下一轮研究假设；Factor端也积累成功与失败案例，辅助重写候选并继续检查三项约束。更新的是假设、候选与外部经验，非LLM模型权重。</t>
         </is>
       </c>
     </row>
-    <row r="8" ht="85" customHeight="1">
-      <c r="A8" t="inlineStr" s="0">
+    <row r="10" ht="103" customHeight="1">
+      <c r="A10" t="inlineStr" s="0">
         <is>
           <t xml:space="preserve">代码与复现边界</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr" s="0">
+      <c r="B10" t="inlineStr" s="0">
         <is>
           <t xml:space="preserve">有源码吗？能直接照仓库复现论文吗？</t>
         </is>
       </c>
-      <c r="C8" t="inlineStr" s="0">
+      <c r="C10" t="inlineStr" s="0">
         <is>
           <t xml:space="preserve">作者公开GitHub仓库，但当前README描述的已是扩展后的DSL/FactorZoo与AgentScope工作流，不能不经核对就当作KDD 2025论文的原版实现；此表依据论文§3–4，未运行论文版本。源码入口：https://github.com/RndmVariableQ/AlphaAgent</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:C8"/>
+  <autoFilter ref="A1:C10"/>
   <hyperlinks>
-    <hyperlink ref="C8" r:id="rId1" tooltip="打开作者的AlphaAgent GitHub仓库"/>
+    <hyperlink ref="C10" r:id="rId1" tooltip="打开原始资料链接"/>
   </hyperlinks>
 </worksheet>
 </file>
--- a/papers/P003/P003_工程复现问题清单_v1.xlsx
+++ b/papers/P003/P003_工程复现问题清单_v1.xlsx
@@ -36,7 +36,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFF1F5F9"/>
+        <fgColor rgb="FFF2F5F9"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -55,13 +55,13 @@
   </cellStyleXfs>
   <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment wrapText="1" vertical="center"/>
+      <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment wrapText="1" vertical="center"/>
+      <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment wrapText="1" vertical="center"/>
+      <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -72,15 +72,15 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C10"/>
+  <dimension ref="A1:C11"/>
   <sheetFormatPr defaultRowHeight="25"/>
   <cols>
     <col min="1" max="1" width="26" customWidth="1"/>
-    <col min="2" max="2" width="54" customWidth="1"/>
-    <col min="3" max="3" width="103" customWidth="1"/>
+    <col min="2" max="2" width="53" customWidth="1"/>
+    <col min="3" max="3" width="92" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="38" customHeight="1">
+    <row r="1" ht="36" customHeight="1">
       <c r="A1" t="inlineStr" s="1">
         <is>
           <t xml:space="preserve">主题</t>
@@ -97,7 +97,7 @@
         </is>
       </c>
     </row>
-    <row r="2" ht="93" customHeight="1">
+    <row r="2" ht="82" customHeight="1">
       <c r="A2" t="inlineStr" s="0">
         <is>
           <t xml:space="preserve">初始研究假设</t>
@@ -114,7 +114,7 @@
         </is>
       </c>
     </row>
-    <row r="3" ht="103" customHeight="1">
+    <row r="3" ht="94" customHeight="1">
       <c r="A3" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">Agent输入与上下文</t>
@@ -131,7 +131,7 @@
         </is>
       </c>
     </row>
-    <row r="4" ht="93" customHeight="1">
+    <row r="4" ht="82" customHeight="1">
       <c r="A4" t="inlineStr" s="0">
         <is>
           <t xml:space="preserve">LLM与Agent分工</t>
@@ -148,7 +148,7 @@
         </is>
       </c>
     </row>
-    <row r="5" ht="93" customHeight="1">
+    <row r="5" ht="82" customHeight="1">
       <c r="A5" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">因子生成格式</t>
@@ -165,7 +165,7 @@
         </is>
       </c>
     </row>
-    <row r="6" ht="93" customHeight="1">
+    <row r="6" ht="94" customHeight="1">
       <c r="A6" t="inlineStr" s="0">
         <is>
           <t xml:space="preserve">三项生成约束</t>
@@ -182,7 +182,7 @@
         </is>
       </c>
     </row>
-    <row r="7" ht="93" customHeight="1">
+    <row r="7" ht="82" customHeight="1">
       <c r="A7" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">质量评价</t>
@@ -199,7 +199,7 @@
         </is>
       </c>
     </row>
-    <row r="8" ht="93" customHeight="1">
+    <row r="8" ht="94" customHeight="1">
       <c r="A8" t="inlineStr" s="0">
         <is>
           <t xml:space="preserve">单因子还是池级增益</t>
@@ -216,7 +216,7 @@
         </is>
       </c>
     </row>
-    <row r="9" ht="93" customHeight="1">
+    <row r="9" ht="94" customHeight="1">
       <c r="A9" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">反馈与自迭代</t>
@@ -233,27 +233,44 @@
         </is>
       </c>
     </row>
-    <row r="10" ht="103" customHeight="1">
+    <row r="10" ht="94" customHeight="1">
       <c r="A10" t="inlineStr" s="0">
         <is>
+          <t xml:space="preserve">搜索调度与优化对象</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr" s="0">
+        <is>
+          <t xml:space="preserve">是否使用Bandit选择因子或模型？模型方案也是Idea Agent提出吗？</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr" s="0">
+        <is>
+          <t xml:space="preserve">没有P006式Bandit双路径；P003主要由Idea Agent提因子研究假设、Factor Agent生成算子表达式、Eval Agent打分反馈。预测模型用于统一训练与评价，不构成LLM自主提出模型架构并与因子研究交替优化的Model分支。</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="108" customHeight="1">
+      <c r="A11" t="inlineStr" s="2">
+        <is>
           <t xml:space="preserve">代码与复现边界</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr" s="0">
+      <c r="B11" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">有源码吗？能直接照仓库复现论文吗？</t>
         </is>
       </c>
-      <c r="C10" t="inlineStr" s="0">
+      <c r="C11" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">作者公开GitHub仓库，但当前README描述的已是扩展后的DSL/FactorZoo与AgentScope工作流，不能不经核对就当作KDD 2025论文的原版实现；此表依据论文§3–4，未运行论文版本。源码入口：https://github.com/RndmVariableQ/AlphaAgent</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:C10"/>
+  <autoFilter ref="A1:C11"/>
   <hyperlinks>
-    <hyperlink ref="C10" r:id="rId1" tooltip="打开原始资料链接"/>
+    <hyperlink ref="C11" r:id="rId1" tooltip="打开相关公开资料"/>
   </hyperlinks>
 </worksheet>
 </file>
--- a/papers/P003/P003_工程复现问题清单_v1.xlsx
+++ b/papers/P003/P003_工程复现问题清单_v1.xlsx
@@ -30,7 +30,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF142B46"/>
+        <fgColor rgb="FF172D48"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -72,12 +72,12 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C11"/>
+  <dimension ref="A1:C10"/>
   <sheetFormatPr defaultRowHeight="25"/>
   <cols>
-    <col min="1" max="1" width="26" customWidth="1"/>
+    <col min="1" max="1" width="27" customWidth="1"/>
     <col min="2" max="2" width="53" customWidth="1"/>
-    <col min="3" max="3" width="92" customWidth="1"/>
+    <col min="3" max="3" width="98" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" ht="36" customHeight="1">
@@ -97,180 +97,163 @@
         </is>
       </c>
     </row>
-    <row r="2" ht="82" customHeight="1">
+    <row r="2" ht="86" customHeight="1">
       <c r="A2" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">初始研究假设</t>
+          <t xml:space="preserve">研究假设与输入</t>
         </is>
       </c>
       <c r="B2" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">最开始谁提出研究方向，Idea Agent 做什么？</t>
+          <t xml:space="preserve">第一条Idea谁给？Idea怎样传给Factor？</t>
         </is>
       </c>
       <c r="C2" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">用户/领域专家给初始方向或市场观察；Idea Agent结合金融知识和反馈，整理成观察、知识依据、经济解释、实现规格四部分的研究假设。</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="94" customHeight="1">
+          <t xml:space="preserve">用户或专家给研究方向/市场观察；Idea Agent整理为观察、知识依据、经济解释、实现规格四部分。Factor结合此假设、金融算子及成败案例写公式；论文未给出可核验的原版逐字Prompt，也无P005式每日市场摘要。</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="78" customHeight="1">
       <c r="A3" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Agent输入与上下文</t>
+          <t xml:space="preserve">LLM与Agent分工</t>
         </is>
       </c>
       <c r="B3" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">市场知识、历史案例怎样进入Factor Agent？是否是结构化Prompt？</t>
+          <t xml:space="preserve">使用什么模型？三个Agent分别负责什么？</t>
         </is>
       </c>
       <c r="C3" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Idea Agent把研究方向或市场观察整理为“观察、知识、经济解释、实现规格”四部分假设；Factor Agent结合假设、金融算子库和成功/失败实现经验生成公式。论文说明了信息结构，但未从论文原版源码核实逐字Prompt装配，也没有P005式每日市场摘要器。</t>
-        </is>
-      </c>
-    </row>
-    <row r="4" ht="82" customHeight="1">
+          <t xml:space="preserve">论文实验使用GPT-3.5-turbo作为基础LLM；Idea提出假设，Factor构造多个因子，Eval负责评价与反馈。原文未报告通过微调更新这些Agent的模型参数。</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="78" customHeight="1">
       <c r="A4" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">LLM与Agent分工</t>
+          <t xml:space="preserve">因子生成格式</t>
         </is>
       </c>
       <c r="B4" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">使用什么模型？三个Agent分别负责什么？</t>
+          <t xml:space="preserve">Factor Agent怎么把Idea变成可执行因子？</t>
         </is>
       </c>
       <c r="C4" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">论文实验使用GPT-3.5-turbo作为基础LLM；Idea提出假设，Factor构造多个因子，Eval负责评价与反馈。原文未报告通过微调更新这些Agent的模型参数。</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="82" customHeight="1">
+          <t xml:space="preserve">调用金融算子库（如滚动均值、最高最低值、条件算子），把原始行情字段与算子组成符号表达式/AST计算树，而非直接自由生成完整Python程序；每个假设可对应多个候选。</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="86" customHeight="1">
       <c r="A5" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">因子生成格式</t>
+          <t xml:space="preserve">三项生成约束</t>
         </is>
       </c>
       <c r="B5" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Factor Agent怎么把Idea变成可执行因子？</t>
+          <t xml:space="preserve">为什么说生成不是随便写公式？</t>
         </is>
       </c>
       <c r="C5" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">调用金融算子库（如滚动均值、最高最低值、条件算子），把原始行情字段与算子组成符号表达式/AST计算树，而非直接自由生成完整Python程序；每个假设可对应多个候选。</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="94" customHeight="1">
+          <t xml:space="preserve">①原创性：将新因子AST与Alpha Zoo既有因子比较最大公共子树，抑制结构重复；②语义一致性：LLM分别判断假设→因子描述、描述→公式是否匹配；③复杂度：限制公式长度、参数与特征数量。</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="78" customHeight="1">
       <c r="A6" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">三项生成约束</t>
+          <t xml:space="preserve">质量评价</t>
         </is>
       </c>
       <c r="B6" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">为什么说生成不是随便写公式？</t>
+          <t xml:space="preserve">Eval Agent具体评什么？</t>
         </is>
       </c>
       <c r="C6" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">①原创性：将新因子AST与Alpha Zoo既有因子比较最大公共子树，抑制结构重复；②语义一致性：LLM分别判断假设→因子描述、描述→公式是否匹配；③复杂度：限制公式长度、参数与特征数量。</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="82" customHeight="1">
+          <t xml:space="preserve">Eval先检查能否执行和数值是否稳定，再用历史数据算IC/RankIC/ICIR及收益风险指标，论文采用Qlib；不是只听LLM打分。</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="78" customHeight="1">
       <c r="A7" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">质量评价</t>
+          <t xml:space="preserve">单因子还是池级增益</t>
         </is>
       </c>
       <c r="B7" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Eval Agent具体评什么？</t>
+          <t xml:space="preserve">这是按单个因子质量筛选，还是按整池新增边际贡献筛选？</t>
         </is>
       </c>
       <c r="C7" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">检查因子可执行性、数值稳定性，并通过历史数据检验预测力（IC/RankIC/ICIR）、收益和风险表现；论文采用Qlib回测。重点是实际计算指标，而非仅由LLM主观判断。</t>
-        </is>
-      </c>
-    </row>
-    <row r="8" ht="94" customHeight="1">
+          <t xml:space="preserve">以各候选的结构原创性、语义对齐、复杂度和单因子表现评价；Alpha Zoo用于相似度参照，未采用P005式整池分数增量ΔΓ。</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="78" customHeight="1">
       <c r="A8" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">单因子还是池级增益</t>
+          <t xml:space="preserve">反馈与自迭代</t>
         </is>
       </c>
       <c r="B8" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">这是按单个因子质量筛选，还是按整池新增边际贡献筛选？</t>
+          <t xml:space="preserve">评价结果究竟怎样进入下一轮？</t>
         </is>
       </c>
       <c r="C8" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">主要检查各候选的AST原创性、假设对齐、复杂度和预测/收益/风险表现；Alpha Zoo用于结构相似度参照，成功失败结果用于经验反馈。论文没有说明使用P005那样的加权组合池评分差ΔΓ决定加入/替换。</t>
-        </is>
-      </c>
-    </row>
-    <row r="9" ht="94" customHeight="1">
+          <t xml:space="preserve">Eval汇总成功/失败及表现反馈给Idea以改写下一轮研究假设；Factor端也积累成功与失败案例，辅助重写候选并继续检查三项约束。更新的是假设、候选与外部经验，非LLM模型权重。</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="78" customHeight="1">
       <c r="A9" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">反馈与自迭代</t>
+          <t xml:space="preserve">搜索调度与优化对象</t>
         </is>
       </c>
       <c r="B9" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">评价结果究竟怎样进入下一轮？</t>
+          <t xml:space="preserve">是否使用Bandit选择因子或模型？模型方案也是Idea Agent提出吗？</t>
         </is>
       </c>
       <c r="C9" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Eval汇总成功/失败及表现反馈给Idea以改写下一轮研究假设；Factor端也积累成功与失败案例，辅助重写候选并继续检查三项约束。更新的是假设、候选与外部经验，非LLM模型权重。</t>
-        </is>
-      </c>
-    </row>
-    <row r="10" ht="94" customHeight="1">
+          <t xml:space="preserve">Idea→Factor→Eval专注因子生成与反馈；没有P006式Bandit因子/模型交替研发，也没有由Idea设计预测模型架构的分支。</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="96" customHeight="1">
       <c r="A10" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">搜索调度与优化对象</t>
+          <t xml:space="preserve">代码与复现边界</t>
         </is>
       </c>
       <c r="B10" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">是否使用Bandit选择因子或模型？模型方案也是Idea Agent提出吗？</t>
+          <t xml:space="preserve">有源码吗？能直接照仓库复现论文吗？</t>
         </is>
       </c>
       <c r="C10" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">没有P006式Bandit双路径；P003主要由Idea Agent提因子研究假设、Factor Agent生成算子表达式、Eval Agent打分反馈。预测模型用于统一训练与评价，不构成LLM自主提出模型架构并与因子研究交替优化的Model分支。</t>
-        </is>
-      </c>
-    </row>
-    <row r="11" ht="108" customHeight="1">
-      <c r="A11" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">代码与复现边界</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">有源码吗？能直接照仓库复现论文吗？</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr" s="2">
-        <is>
           <t xml:space="preserve">作者公开GitHub仓库，但当前README描述的已是扩展后的DSL/FactorZoo与AgentScope工作流，不能不经核对就当作KDD 2025论文的原版实现；此表依据论文§3–4，未运行论文版本。源码入口：https://github.com/RndmVariableQ/AlphaAgent</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:C11"/>
+  <autoFilter ref="A1:C10"/>
   <hyperlinks>
-    <hyperlink ref="C11" r:id="rId1" tooltip="打开相关公开资料"/>
+    <hyperlink ref="C10" r:id="rId1" tooltip="打开相关来源或机制图解"/>
   </hyperlinks>
 </worksheet>
 </file>